--- a/benchmarks/business_workflow_lab/templates/quote_template.xlsx
+++ b/benchmarks/business_workflow_lab/templates/quote_template.xlsx
@@ -828,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1038,46 +1038,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AmountTWD</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>原幣金額 × 匯率（fx_rates.csv），四捨五入 ROUND_HALF_UP 至兩位小數；不同幣別的原幣金額不可直接相加。</t>
+          <t>欄寬、凍結窗格、自動篩選、字型與填色保留模板設定，不要調整或自動調整欄寬。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Quotes</t>
+          <t>All detail sheets</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>Missing values</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>QuoteID: text (文字，保留前導零)</t>
+          <t>來源沒有的值留空（空白儲存格），不要填 N/A、0 或自行推測的值。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quotes</t>
+          <t>All sheets</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>AmountTWD</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>CustomerID: text (文字，保留前導零)</t>
+          <t>原幣金額 × 匯率（fx_rates.csv），四捨五入 ROUND_HALF_UP 至兩位小數；不同幣別的原幣金額不可直接相加。</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>ProjectID: text (文字，保留前導零)</t>
+          <t>QuoteID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>QuoteDate: date YYYY-MM-DD</t>
+          <t>CustomerID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>ValidUntil: date YYYY-MM-DD</t>
+          <t>ProjectID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Status: text</t>
+          <t>QuoteDate: date YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Currency: text</t>
+          <t>ValidUntil: date YYYY-MM-DD</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Subtotal: number, 2 decimals (0.00)</t>
+          <t>Status: text</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>DiscountPercent: number</t>
+          <t>Currency: text</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>NetAmount: number, 2 decimals (0.00)</t>
+          <t>Subtotal: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
@@ -1225,46 +1225,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>NetAmountTWD: number, 2 decimals (0.00)</t>
+          <t>DiscountPercent: number</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lines</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>QuoteID: text (文字，保留前導零)</t>
+          <t>NetAmount: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lines</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>ProductID: text (文字，保留前導零)</t>
+          <t>NetAmountTWD: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>ProductName: text</t>
+          <t>QuoteID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Quantity: number</t>
+          <t>ProductID: text (文字，保留前導零)</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>UnitPrice: number, 2 decimals (0.00)</t>
+          <t>ProductName: text</t>
         </is>
       </c>
     </row>
@@ -1327,29 +1327,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>LineAmount: number, 2 decimals (0.00)</t>
+          <t>Quantity: number</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Quotes</t>
+          <t>Lines</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>DiscountPercent 為百分比數字，例如 5 代表 5%。</t>
+          <t>UnitPrice: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
@@ -1361,44 +1361,78 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>每個明細列都要有對應的 QuoteID（與 Quotes 工作表 join）。</t>
+          <t>LineAmount: number, 2 decimals (0.00)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>公式 =SUM(Quotes!K5:K{最後資料列})：Quotes 的 NetAmountTWD 合計；填入資料後把範圍延伸到最後一列，零筆時保留 K5:K5。</t>
+          <t>DiscountPercent 為百分比數字，例如 5 代表 5%。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>每個明細列都要有對應的 QuoteID（與 Quotes 工作表 join）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>公式 =SUM(Quotes!K5:K{最後資料列})：Quotes 的 NetAmountTWD 合計；填入資料後把範圍延伸到最後一列，零筆時保留 K5:K5。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>A4:F4 / row 5+</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>彙總表：Group、SubGroup 為分組鍵（依題目要求，例如 Status、Currency、EmployeeID、Category；不用時留空），Currency 為原幣，Amount 為該組原幣合計，AmountTWD 為該組 TWD 合計，Count 為筆數；全部 TWD 總額不得混加不同原幣。</t>
         </is>
